--- a/informes_data/Euroleague/2025-26/Regular_Season/aggregate_individual/AGG_IND_CRVENA ZVEZDA MERIDIANBET BELGRADE.xlsx
+++ b/informes_data/Euroleague/2025-26/Regular_Season/aggregate_individual/AGG_IND_CRVENA ZVEZDA MERIDIANBET BELGRADE.xlsx
@@ -565,13 +565,13 @@
         <v>33</v>
       </c>
       <c r="D2" t="n">
-        <v>74.43469999999999</v>
+        <v>63.6623</v>
       </c>
       <c r="E2" t="n">
-        <v>52.0344</v>
+        <v>46.9658</v>
       </c>
       <c r="F2" t="n">
-        <v>22.4001</v>
+        <v>16.6963</v>
       </c>
       <c r="G2" t="n">
         <v>15.6393</v>
@@ -610,13 +610,13 @@
         <v>67.4982</v>
       </c>
       <c r="S2" t="n">
-        <v>35.6803</v>
+        <v>24.9076</v>
       </c>
       <c r="T2" t="n">
-        <v>16.8891</v>
+        <v>11.8205</v>
       </c>
       <c r="U2" t="n">
-        <v>18.7907</v>
+        <v>13.0872</v>
       </c>
       <c r="V2" t="n">
         <v>29.6098</v>
@@ -643,13 +643,13 @@
         <v>30</v>
       </c>
       <c r="D3" t="n">
-        <v>69.8497</v>
+        <v>46.2617</v>
       </c>
       <c r="E3" t="n">
-        <v>75.5095</v>
+        <v>50.7042</v>
       </c>
       <c r="F3" t="n">
-        <v>-5.6599</v>
+        <v>-4.4422</v>
       </c>
       <c r="G3" t="n">
         <v>22.9127</v>
@@ -688,13 +688,13 @@
         <v>31.546</v>
       </c>
       <c r="S3" t="n">
-        <v>46.1235</v>
+        <v>22.5351</v>
       </c>
       <c r="T3" t="n">
-        <v>42.2981</v>
+        <v>17.4926</v>
       </c>
       <c r="U3" t="n">
-        <v>3.8251</v>
+        <v>5.0427</v>
       </c>
       <c r="V3" t="n">
         <v>-7.5365</v>
@@ -721,13 +721,13 @@
         <v>37</v>
       </c>
       <c r="D4" t="n">
-        <v>25.2467</v>
+        <v>27.446</v>
       </c>
       <c r="E4" t="n">
-        <v>17.3391</v>
+        <v>10.7569</v>
       </c>
       <c r="F4" t="n">
-        <v>7.907399999999999</v>
+        <v>16.6892</v>
       </c>
       <c r="G4" t="n">
         <v>-20.9053</v>
@@ -766,13 +766,13 @@
         <v>60.772</v>
       </c>
       <c r="S4" t="n">
-        <v>17.1761</v>
+        <v>19.3756</v>
       </c>
       <c r="T4" t="n">
-        <v>20.8602</v>
+        <v>14.2782</v>
       </c>
       <c r="U4" t="n">
-        <v>-3.6842</v>
+        <v>5.0977</v>
       </c>
       <c r="V4" t="n">
         <v>0.6779000000000001</v>
@@ -787,7 +787,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>O. DOBRIC</t>
+          <t>C. MILLER-MCINTYRE</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -796,76 +796,76 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>25</v>
+        <v>37</v>
       </c>
       <c r="D5" t="n">
-        <v>13.2529</v>
+        <v>17.8259</v>
       </c>
       <c r="E5" t="n">
-        <v>6.336900000000001</v>
+        <v>2.649000000000001</v>
       </c>
       <c r="F5" t="n">
-        <v>6.9162</v>
+        <v>15.1767</v>
       </c>
       <c r="G5" t="n">
-        <v>-6.372900000000001</v>
+        <v>56.7691</v>
       </c>
       <c r="H5" t="n">
-        <v>-8.567400000000001</v>
+        <v>23.9438</v>
       </c>
       <c r="I5" t="n">
-        <v>2.1945</v>
+        <v>32.8256</v>
       </c>
       <c r="J5" t="n">
-        <v>5.1417</v>
+        <v>104.8772</v>
       </c>
       <c r="K5" t="n">
-        <v>-1.7989</v>
+        <v>54.6599</v>
       </c>
       <c r="L5" t="n">
-        <v>6.9411</v>
+        <v>50.2177</v>
       </c>
       <c r="M5" t="n">
-        <v>-11.5147</v>
+        <v>-48.1081</v>
       </c>
       <c r="N5" t="n">
-        <v>-6.7683</v>
+        <v>-30.7156</v>
       </c>
       <c r="O5" t="n">
-        <v>-4.7463</v>
+        <v>-17.3926</v>
       </c>
       <c r="P5" t="n">
-        <v>17.3968</v>
+        <v>-33.1691</v>
       </c>
       <c r="Q5" t="n">
-        <v>-7.8865</v>
+        <v>-120.6149</v>
       </c>
       <c r="R5" t="n">
-        <v>25.2832</v>
+        <v>87.4461</v>
       </c>
       <c r="S5" t="n">
-        <v>1.472</v>
+        <v>13.3215</v>
       </c>
       <c r="T5" t="n">
-        <v>4.7925</v>
+        <v>4.7348</v>
       </c>
       <c r="U5" t="n">
-        <v>-3.3205</v>
+        <v>8.5862</v>
       </c>
       <c r="V5" t="n">
-        <v>0.7575000000000003</v>
+        <v>-19.0957</v>
       </c>
       <c r="W5" t="n">
-        <v>4.2888</v>
+        <v>13.6512</v>
       </c>
       <c r="X5" t="n">
-        <v>-3.5313</v>
+        <v>-32.7469</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>D. MOTIEJUNAS</t>
+          <t>O. DOBRIC</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -874,76 +874,76 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D6" t="n">
-        <v>12.6098</v>
+        <v>15.8416</v>
       </c>
       <c r="E6" t="n">
-        <v>8.0085</v>
+        <v>6.8282</v>
       </c>
       <c r="F6" t="n">
-        <v>4.6013</v>
+        <v>9.013199999999999</v>
       </c>
       <c r="G6" t="n">
-        <v>1.684799999999998</v>
+        <v>-6.372900000000001</v>
       </c>
       <c r="H6" t="n">
-        <v>1.7675</v>
+        <v>-8.567400000000001</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.08239999999999958</v>
+        <v>2.1945</v>
       </c>
       <c r="J6" t="n">
-        <v>15.9486</v>
+        <v>5.1417</v>
       </c>
       <c r="K6" t="n">
-        <v>10.8666</v>
+        <v>-1.7989</v>
       </c>
       <c r="L6" t="n">
-        <v>5.082</v>
+        <v>6.9411</v>
       </c>
       <c r="M6" t="n">
-        <v>-14.2639</v>
+        <v>-11.5147</v>
       </c>
       <c r="N6" t="n">
-        <v>-9.099500000000001</v>
+        <v>-6.7683</v>
       </c>
       <c r="O6" t="n">
-        <v>-5.1643</v>
+        <v>-4.7463</v>
       </c>
       <c r="P6" t="n">
-        <v>6.2629</v>
+        <v>17.3968</v>
       </c>
       <c r="Q6" t="n">
-        <v>-21.34</v>
+        <v>-7.8865</v>
       </c>
       <c r="R6" t="n">
-        <v>27.6026</v>
+        <v>25.2832</v>
       </c>
       <c r="S6" t="n">
-        <v>4.002000000000001</v>
+        <v>4.0606</v>
       </c>
       <c r="T6" t="n">
-        <v>4.6355</v>
+        <v>5.2843</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.6335</v>
+        <v>-1.2234</v>
       </c>
       <c r="V6" t="n">
-        <v>0.6605000000000003</v>
+        <v>0.7575000000000003</v>
       </c>
       <c r="W6" t="n">
-        <v>8.764100000000001</v>
+        <v>4.2888</v>
       </c>
       <c r="X6" t="n">
-        <v>-8.1037</v>
+        <v>-3.5313</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>D. DAVIDOVAC</t>
+          <t>D. MOTIEJUNAS</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -952,76 +952,76 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="D7" t="n">
-        <v>9.110500000000002</v>
+        <v>13.579</v>
       </c>
       <c r="E7" t="n">
-        <v>7.649299999999999</v>
+        <v>6.377000000000001</v>
       </c>
       <c r="F7" t="n">
-        <v>1.4612</v>
+        <v>7.202200000000001</v>
       </c>
       <c r="G7" t="n">
-        <v>-6.287</v>
+        <v>1.684799999999998</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.6503999999999998</v>
+        <v>1.7675</v>
       </c>
       <c r="I7" t="n">
-        <v>-5.6366</v>
+        <v>-0.08239999999999958</v>
       </c>
       <c r="J7" t="n">
-        <v>8.628400000000001</v>
+        <v>15.9486</v>
       </c>
       <c r="K7" t="n">
-        <v>5.6307</v>
+        <v>10.8666</v>
       </c>
       <c r="L7" t="n">
-        <v>2.9975</v>
+        <v>5.082</v>
       </c>
       <c r="M7" t="n">
-        <v>-14.9155</v>
+        <v>-14.2639</v>
       </c>
       <c r="N7" t="n">
-        <v>-6.2813</v>
+        <v>-9.099500000000001</v>
       </c>
       <c r="O7" t="n">
-        <v>-8.6342</v>
+        <v>-5.1643</v>
       </c>
       <c r="P7" t="n">
-        <v>16.4686</v>
+        <v>6.2629</v>
       </c>
       <c r="Q7" t="n">
-        <v>-7.1908</v>
+        <v>-21.34</v>
       </c>
       <c r="R7" t="n">
-        <v>23.6593</v>
+        <v>27.6026</v>
       </c>
       <c r="S7" t="n">
-        <v>1.5299</v>
+        <v>4.9714</v>
       </c>
       <c r="T7" t="n">
-        <v>3.105700000000001</v>
+        <v>3.0038</v>
       </c>
       <c r="U7" t="n">
-        <v>-1.5758</v>
+        <v>1.9677</v>
       </c>
       <c r="V7" t="n">
-        <v>-2.6009</v>
+        <v>0.6605000000000003</v>
       </c>
       <c r="W7" t="n">
-        <v>3.1059</v>
+        <v>8.764100000000001</v>
       </c>
       <c r="X7" t="n">
-        <v>-5.7068</v>
+        <v>-8.1037</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>J. BOLOMBOY</t>
+          <t>D. DAVIDOVAC</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1030,70 +1030,70 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="D8" t="n">
-        <v>8.713799999999999</v>
+        <v>11.543</v>
       </c>
       <c r="E8" t="n">
-        <v>9.2081</v>
+        <v>8.365</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.4943999999999995</v>
+        <v>3.1776</v>
       </c>
       <c r="G8" t="n">
-        <v>-5.8329</v>
+        <v>-6.287</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.3762999999999993</v>
+        <v>-0.6503999999999998</v>
       </c>
       <c r="I8" t="n">
-        <v>-5.4563</v>
+        <v>-5.6366</v>
       </c>
       <c r="J8" t="n">
-        <v>9.117599999999999</v>
+        <v>8.628400000000001</v>
       </c>
       <c r="K8" t="n">
-        <v>3.918</v>
+        <v>5.6307</v>
       </c>
       <c r="L8" t="n">
-        <v>5.1994</v>
+        <v>2.9975</v>
       </c>
       <c r="M8" t="n">
-        <v>-14.9501</v>
+        <v>-14.9155</v>
       </c>
       <c r="N8" t="n">
-        <v>-4.2943</v>
+        <v>-6.2813</v>
       </c>
       <c r="O8" t="n">
-        <v>-10.656</v>
+        <v>-8.6342</v>
       </c>
       <c r="P8" t="n">
-        <v>-2.3196</v>
+        <v>16.4686</v>
       </c>
       <c r="Q8" t="n">
-        <v>-19.2523</v>
+        <v>-7.1908</v>
       </c>
       <c r="R8" t="n">
-        <v>16.9326</v>
+        <v>23.6593</v>
       </c>
       <c r="S8" t="n">
-        <v>21.2656</v>
+        <v>3.9621</v>
       </c>
       <c r="T8" t="n">
-        <v>16.0948</v>
+        <v>3.8213</v>
       </c>
       <c r="U8" t="n">
-        <v>5.1705</v>
+        <v>0.1408999999999999</v>
       </c>
       <c r="V8" t="n">
-        <v>-4.3995</v>
+        <v>-2.6009</v>
       </c>
       <c r="W8" t="n">
-        <v>3.2477</v>
+        <v>3.1059</v>
       </c>
       <c r="X8" t="n">
-        <v>-7.6472</v>
+        <v>-5.7068</v>
       </c>
     </row>
     <row r="9">
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>2.8287</v>
+        <v>2.6668</v>
       </c>
       <c r="E9" t="n">
-        <v>4.2204</v>
+        <v>3.8233</v>
       </c>
       <c r="F9" t="n">
-        <v>-1.3917</v>
+        <v>-1.1564</v>
       </c>
       <c r="G9" t="n">
         <v>2.8751</v>
@@ -1156,13 +1156,13 @@
         <v>1.3917</v>
       </c>
       <c r="S9" t="n">
-        <v>0.7938</v>
+        <v>0.6319</v>
       </c>
       <c r="T9" t="n">
-        <v>1.1325</v>
+        <v>0.7354000000000001</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.3387</v>
+        <v>-0.1034</v>
       </c>
       <c r="V9" t="n">
         <v>-1.0722</v>
@@ -1177,7 +1177,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>O. RADOSIC</t>
+          <t>S. MILJENOVIC</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1186,76 +1186,76 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="D10" t="n">
-        <v>0.3892</v>
+        <v>0.5411000000000006</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.0747</v>
+        <v>-0.8117000000000001</v>
       </c>
       <c r="F10" t="n">
-        <v>0.4639</v>
+        <v>1.3528</v>
       </c>
       <c r="G10" t="n">
-        <v>0</v>
+        <v>-5.6593</v>
       </c>
       <c r="H10" t="n">
-        <v>0</v>
+        <v>-2.35</v>
       </c>
       <c r="I10" t="n">
-        <v>0</v>
+        <v>-3.3091</v>
       </c>
       <c r="J10" t="n">
-        <v>0</v>
+        <v>-2.049</v>
       </c>
       <c r="K10" t="n">
-        <v>0</v>
+        <v>-1.122</v>
       </c>
       <c r="L10" t="n">
-        <v>0</v>
+        <v>-0.9271000000000001</v>
       </c>
       <c r="M10" t="n">
-        <v>0</v>
+        <v>-3.6103</v>
       </c>
       <c r="N10" t="n">
-        <v>0</v>
+        <v>-1.2283</v>
       </c>
       <c r="O10" t="n">
-        <v>0</v>
+        <v>-2.3818</v>
       </c>
       <c r="P10" t="n">
-        <v>0.4639</v>
+        <v>2.5515</v>
       </c>
       <c r="Q10" t="n">
-        <v>0</v>
+        <v>-4.6392</v>
       </c>
       <c r="R10" t="n">
-        <v>0.4639</v>
+        <v>7.1907</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.0747</v>
+        <v>1.252</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.0747</v>
+        <v>0.6259999999999999</v>
       </c>
       <c r="U10" t="n">
-        <v>0</v>
+        <v>0.626</v>
       </c>
       <c r="V10" t="n">
-        <v>0</v>
+        <v>2.3969</v>
       </c>
       <c r="W10" t="n">
-        <v>0</v>
+        <v>5.2503</v>
       </c>
       <c r="X10" t="n">
-        <v>0</v>
+        <v>-2.8534</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>J. RIVERO</t>
+          <t>O. RADOSIC</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1264,76 +1264,76 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-1.3991</v>
+        <v>0.3892</v>
       </c>
       <c r="E11" t="n">
-        <v>2.365699999999999</v>
+        <v>-0.0747</v>
       </c>
       <c r="F11" t="n">
-        <v>-3.7645</v>
+        <v>0.4639</v>
       </c>
       <c r="G11" t="n">
-        <v>-4.9056</v>
+        <v>0</v>
       </c>
       <c r="H11" t="n">
-        <v>-3.2931</v>
+        <v>0</v>
       </c>
       <c r="I11" t="n">
-        <v>-1.6125</v>
+        <v>0</v>
       </c>
       <c r="J11" t="n">
-        <v>1.0537</v>
+        <v>0</v>
       </c>
       <c r="K11" t="n">
-        <v>0.3912</v>
+        <v>0</v>
       </c>
       <c r="L11" t="n">
-        <v>0.6624</v>
+        <v>0</v>
       </c>
       <c r="M11" t="n">
-        <v>-5.9592</v>
+        <v>0</v>
       </c>
       <c r="N11" t="n">
-        <v>-3.6843</v>
+        <v>0</v>
       </c>
       <c r="O11" t="n">
-        <v>-2.2749</v>
+        <v>0</v>
       </c>
       <c r="P11" t="n">
-        <v>3.2473</v>
+        <v>0.4639</v>
       </c>
       <c r="Q11" t="n">
-        <v>-3.7113</v>
+        <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>6.958699999999999</v>
+        <v>0.4639</v>
       </c>
       <c r="S11" t="n">
-        <v>2.1201</v>
+        <v>-0.0747</v>
       </c>
       <c r="T11" t="n">
-        <v>1.3812</v>
+        <v>-0.0747</v>
       </c>
       <c r="U11" t="n">
-        <v>0.7388</v>
+        <v>0</v>
       </c>
       <c r="V11" t="n">
-        <v>-1.8608</v>
+        <v>0</v>
       </c>
       <c r="W11" t="n">
-        <v>3.642</v>
+        <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>-5.502800000000001</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>S. MILJENOVIC</t>
+          <t>J. BOLOMBOY</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1342,76 +1342,76 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="D12" t="n">
-        <v>-2.2852</v>
+        <v>-2.5263</v>
       </c>
       <c r="E12" t="n">
-        <v>-3.2336</v>
+        <v>0.4993000000000003</v>
       </c>
       <c r="F12" t="n">
-        <v>0.9482999999999999</v>
+        <v>-3.0257</v>
       </c>
       <c r="G12" t="n">
-        <v>-5.6593</v>
+        <v>-5.8329</v>
       </c>
       <c r="H12" t="n">
-        <v>-2.35</v>
+        <v>-0.3762999999999993</v>
       </c>
       <c r="I12" t="n">
-        <v>-3.3091</v>
+        <v>-5.4563</v>
       </c>
       <c r="J12" t="n">
-        <v>-2.049</v>
+        <v>9.117599999999999</v>
       </c>
       <c r="K12" t="n">
-        <v>-1.122</v>
+        <v>3.918</v>
       </c>
       <c r="L12" t="n">
-        <v>-0.9271000000000001</v>
+        <v>5.1994</v>
       </c>
       <c r="M12" t="n">
-        <v>-3.6103</v>
+        <v>-14.9501</v>
       </c>
       <c r="N12" t="n">
-        <v>-1.2283</v>
+        <v>-4.2943</v>
       </c>
       <c r="O12" t="n">
-        <v>-2.3818</v>
+        <v>-10.656</v>
       </c>
       <c r="P12" t="n">
-        <v>2.5515</v>
+        <v>-2.3196</v>
       </c>
       <c r="Q12" t="n">
-        <v>-4.6392</v>
+        <v>-19.2523</v>
       </c>
       <c r="R12" t="n">
-        <v>7.1907</v>
+        <v>16.9326</v>
       </c>
       <c r="S12" t="n">
-        <v>-1.5745</v>
+        <v>10.0252</v>
       </c>
       <c r="T12" t="n">
-        <v>-1.7958</v>
+        <v>7.386</v>
       </c>
       <c r="U12" t="n">
-        <v>0.2215999999999999</v>
+        <v>2.6393</v>
       </c>
       <c r="V12" t="n">
-        <v>2.3969</v>
+        <v>-4.3995</v>
       </c>
       <c r="W12" t="n">
-        <v>5.2503</v>
+        <v>3.2477</v>
       </c>
       <c r="X12" t="n">
-        <v>-2.8534</v>
+        <v>-7.6472</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>C. MILLER-MCINTYRE</t>
+          <t>J. RIVERO</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1420,76 +1420,76 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>37</v>
+        <v>8</v>
       </c>
       <c r="D13" t="n">
-        <v>-3.520099999999999</v>
+        <v>-2.8349</v>
       </c>
       <c r="E13" t="n">
-        <v>-15.7628</v>
+        <v>0.9069000000000003</v>
       </c>
       <c r="F13" t="n">
-        <v>12.2424</v>
+        <v>-3.7418</v>
       </c>
       <c r="G13" t="n">
-        <v>56.7691</v>
+        <v>-4.9056</v>
       </c>
       <c r="H13" t="n">
-        <v>23.9438</v>
+        <v>-3.2931</v>
       </c>
       <c r="I13" t="n">
-        <v>32.8256</v>
+        <v>-1.6125</v>
       </c>
       <c r="J13" t="n">
-        <v>104.8772</v>
+        <v>1.0537</v>
       </c>
       <c r="K13" t="n">
-        <v>54.6599</v>
+        <v>0.3912</v>
       </c>
       <c r="L13" t="n">
-        <v>50.2177</v>
+        <v>0.6624</v>
       </c>
       <c r="M13" t="n">
-        <v>-48.1081</v>
+        <v>-5.9592</v>
       </c>
       <c r="N13" t="n">
-        <v>-30.7156</v>
+        <v>-3.6843</v>
       </c>
       <c r="O13" t="n">
-        <v>-17.3926</v>
+        <v>-2.2749</v>
       </c>
       <c r="P13" t="n">
-        <v>-33.1691</v>
+        <v>3.2473</v>
       </c>
       <c r="Q13" t="n">
-        <v>-120.6149</v>
+        <v>-3.7113</v>
       </c>
       <c r="R13" t="n">
-        <v>87.4461</v>
+        <v>6.958699999999999</v>
       </c>
       <c r="S13" t="n">
-        <v>-8.0246</v>
+        <v>0.6841999999999999</v>
       </c>
       <c r="T13" t="n">
-        <v>-13.6767</v>
+        <v>-0.07759999999999995</v>
       </c>
       <c r="U13" t="n">
-        <v>5.6518</v>
+        <v>0.7616999999999999</v>
       </c>
       <c r="V13" t="n">
-        <v>-19.0957</v>
+        <v>-1.8608</v>
       </c>
       <c r="W13" t="n">
-        <v>13.6512</v>
+        <v>3.642</v>
       </c>
       <c r="X13" t="n">
-        <v>-32.7469</v>
+        <v>-5.502800000000001</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>U. PLAVSIC</t>
+          <t>J. NWORA</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1498,76 +1498,76 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>7</v>
+        <v>32</v>
       </c>
       <c r="D14" t="n">
-        <v>-4.7238</v>
+        <v>-3.614699999999999</v>
       </c>
       <c r="E14" t="n">
-        <v>-3.2771</v>
+        <v>-14.3137</v>
       </c>
       <c r="F14" t="n">
-        <v>-1.4467</v>
+        <v>10.6992</v>
       </c>
       <c r="G14" t="n">
-        <v>-3.8835</v>
+        <v>-18.5596</v>
       </c>
       <c r="H14" t="n">
-        <v>-3.114</v>
+        <v>-10.7852</v>
       </c>
       <c r="I14" t="n">
-        <v>-0.7693999999999999</v>
+        <v>-7.774000000000001</v>
       </c>
       <c r="J14" t="n">
-        <v>-1.0454</v>
+        <v>22.1501</v>
       </c>
       <c r="K14" t="n">
-        <v>-1.9655</v>
+        <v>14.7049</v>
       </c>
       <c r="L14" t="n">
-        <v>0.9200999999999999</v>
+        <v>7.4454</v>
       </c>
       <c r="M14" t="n">
-        <v>-2.838</v>
+        <v>-40.7096</v>
       </c>
       <c r="N14" t="n">
-        <v>-1.1485</v>
+        <v>-25.4903</v>
       </c>
       <c r="O14" t="n">
-        <v>-1.6896</v>
+        <v>-15.2194</v>
       </c>
       <c r="P14" t="n">
-        <v>-3.4793</v>
+        <v>-17.3964</v>
       </c>
       <c r="Q14" t="n">
-        <v>-5.103</v>
+        <v>-84.89449999999999</v>
       </c>
       <c r="R14" t="n">
-        <v>1.6238</v>
+        <v>67.4982</v>
       </c>
       <c r="S14" t="n">
-        <v>3.4587</v>
+        <v>10.8345</v>
       </c>
       <c r="T14" t="n">
-        <v>2.446</v>
+        <v>2.9276</v>
       </c>
       <c r="U14" t="n">
-        <v>1.0125</v>
+        <v>7.9075</v>
       </c>
       <c r="V14" t="n">
-        <v>-0.8197</v>
+        <v>21.5061</v>
       </c>
       <c r="W14" t="n">
-        <v>0.4254</v>
+        <v>45.5024</v>
       </c>
       <c r="X14" t="n">
-        <v>-1.2451</v>
+        <v>-23.9963</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>D. GRAHAM</t>
+          <t>J. BUTLER</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1576,76 +1576,76 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>7</v>
+        <v>30</v>
       </c>
       <c r="D15" t="n">
-        <v>-12.6886</v>
+        <v>-6.059400000000001</v>
       </c>
       <c r="E15" t="n">
-        <v>-14.2392</v>
+        <v>10.9994</v>
       </c>
       <c r="F15" t="n">
-        <v>1.5506</v>
+        <v>-17.0589</v>
       </c>
       <c r="G15" t="n">
-        <v>-6.3892</v>
+        <v>20.1471</v>
       </c>
       <c r="H15" t="n">
-        <v>-1.7681</v>
+        <v>9.713800000000001</v>
       </c>
       <c r="I15" t="n">
-        <v>-4.6212</v>
+        <v>10.4333</v>
       </c>
       <c r="J15" t="n">
-        <v>-4.8565</v>
+        <v>47.6217</v>
       </c>
       <c r="K15" t="n">
-        <v>-1.7806</v>
+        <v>23.5469</v>
       </c>
       <c r="L15" t="n">
-        <v>-3.0759</v>
+        <v>24.0748</v>
       </c>
       <c r="M15" t="n">
-        <v>-1.5327</v>
+        <v>-27.4748</v>
       </c>
       <c r="N15" t="n">
-        <v>0.01269999999999993</v>
+        <v>-13.8332</v>
       </c>
       <c r="O15" t="n">
-        <v>-1.5453</v>
+        <v>-13.6415</v>
       </c>
       <c r="P15" t="n">
-        <v>-0.9277</v>
+        <v>-26.2106</v>
       </c>
       <c r="Q15" t="n">
-        <v>-6.9587</v>
+        <v>-67.0346</v>
       </c>
       <c r="R15" t="n">
-        <v>6.0309</v>
+        <v>40.8241</v>
       </c>
       <c r="S15" t="n">
-        <v>-2.1859</v>
+        <v>12.1131</v>
       </c>
       <c r="T15" t="n">
-        <v>-1.3831</v>
+        <v>6.5883</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.8031</v>
+        <v>5.5248</v>
       </c>
       <c r="V15" t="n">
-        <v>-3.1855</v>
+        <v>-12.1089</v>
       </c>
       <c r="W15" t="n">
-        <v>-1.0411</v>
+        <v>23.8235</v>
       </c>
       <c r="X15" t="n">
-        <v>-2.1444</v>
+        <v>-35.9324</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>J. NWORA</t>
+          <t>U. PLAVSIC</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1654,70 +1654,70 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>32</v>
+        <v>7</v>
       </c>
       <c r="D16" t="n">
-        <v>-17.9029</v>
+        <v>-6.4849</v>
       </c>
       <c r="E16" t="n">
-        <v>-29.5014</v>
+        <v>-4.735799999999999</v>
       </c>
       <c r="F16" t="n">
-        <v>11.5988</v>
+        <v>-1.7491</v>
       </c>
       <c r="G16" t="n">
-        <v>-18.5596</v>
+        <v>-3.8835</v>
       </c>
       <c r="H16" t="n">
-        <v>-10.7852</v>
+        <v>-3.114</v>
       </c>
       <c r="I16" t="n">
-        <v>-7.774000000000001</v>
+        <v>-0.7693999999999999</v>
       </c>
       <c r="J16" t="n">
-        <v>22.1501</v>
+        <v>-1.0454</v>
       </c>
       <c r="K16" t="n">
-        <v>14.7049</v>
+        <v>-1.9655</v>
       </c>
       <c r="L16" t="n">
-        <v>7.4454</v>
+        <v>0.9200999999999999</v>
       </c>
       <c r="M16" t="n">
-        <v>-40.7096</v>
+        <v>-2.838</v>
       </c>
       <c r="N16" t="n">
-        <v>-25.4903</v>
+        <v>-1.1485</v>
       </c>
       <c r="O16" t="n">
-        <v>-15.2194</v>
+        <v>-1.6896</v>
       </c>
       <c r="P16" t="n">
-        <v>-17.3964</v>
+        <v>-3.4793</v>
       </c>
       <c r="Q16" t="n">
-        <v>-84.89449999999999</v>
+        <v>-5.103</v>
       </c>
       <c r="R16" t="n">
-        <v>67.4982</v>
+        <v>1.6238</v>
       </c>
       <c r="S16" t="n">
-        <v>-3.4536</v>
+        <v>1.6975</v>
       </c>
       <c r="T16" t="n">
-        <v>-12.2603</v>
+        <v>0.9872</v>
       </c>
       <c r="U16" t="n">
-        <v>8.806800000000001</v>
+        <v>0.71</v>
       </c>
       <c r="V16" t="n">
-        <v>21.5061</v>
+        <v>-0.8197</v>
       </c>
       <c r="W16" t="n">
-        <v>45.5024</v>
+        <v>0.4254</v>
       </c>
       <c r="X16" t="n">
-        <v>-23.9963</v>
+        <v>-1.2451</v>
       </c>
     </row>
     <row r="17">
@@ -1735,13 +1735,13 @@
         <v>37</v>
       </c>
       <c r="D17" t="n">
-        <v>-18.2203</v>
+        <v>-7.472900000000001</v>
       </c>
       <c r="E17" t="n">
-        <v>-21.3292</v>
+        <v>-16.6075</v>
       </c>
       <c r="F17" t="n">
-        <v>3.1084</v>
+        <v>9.1347</v>
       </c>
       <c r="G17" t="n">
         <v>0.7354000000000001</v>
@@ -1780,13 +1780,13 @@
         <v>59.8439</v>
       </c>
       <c r="S17" t="n">
-        <v>4.8819</v>
+        <v>15.6295</v>
       </c>
       <c r="T17" t="n">
-        <v>4.4685</v>
+        <v>9.19</v>
       </c>
       <c r="U17" t="n">
-        <v>0.4133999999999998</v>
+        <v>6.4397</v>
       </c>
       <c r="V17" t="n">
         <v>-15.7198</v>
@@ -1801,7 +1801,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>T. CARTER</t>
+          <t>D. GRAHAM</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1810,76 +1810,76 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="D18" t="n">
-        <v>-18.8906</v>
+        <v>-10.3199</v>
       </c>
       <c r="E18" t="n">
-        <v>-17.4003</v>
+        <v>-12.3637</v>
       </c>
       <c r="F18" t="n">
-        <v>-1.4904</v>
+        <v>2.044</v>
       </c>
       <c r="G18" t="n">
-        <v>-10.8911</v>
+        <v>-6.3892</v>
       </c>
       <c r="H18" t="n">
-        <v>-6.865600000000001</v>
+        <v>-1.7681</v>
       </c>
       <c r="I18" t="n">
-        <v>-4.025300000000001</v>
+        <v>-4.6212</v>
       </c>
       <c r="J18" t="n">
-        <v>-4.6676</v>
+        <v>-4.8565</v>
       </c>
       <c r="K18" t="n">
-        <v>-2.4614</v>
+        <v>-1.7806</v>
       </c>
       <c r="L18" t="n">
-        <v>-2.206</v>
+        <v>-3.0759</v>
       </c>
       <c r="M18" t="n">
-        <v>-6.2237</v>
+        <v>-1.5327</v>
       </c>
       <c r="N18" t="n">
-        <v>-4.4041</v>
+        <v>0.01269999999999993</v>
       </c>
       <c r="O18" t="n">
-        <v>-1.8195</v>
+        <v>-1.5453</v>
       </c>
       <c r="P18" t="n">
-        <v>-2.5515</v>
+        <v>-0.9277</v>
       </c>
       <c r="Q18" t="n">
-        <v>-14.3811</v>
+        <v>-6.9587</v>
       </c>
       <c r="R18" t="n">
-        <v>11.8297</v>
+        <v>6.0309</v>
       </c>
       <c r="S18" t="n">
-        <v>-2.6258</v>
+        <v>0.1828</v>
       </c>
       <c r="T18" t="n">
-        <v>-1.0324</v>
+        <v>0.4924</v>
       </c>
       <c r="U18" t="n">
-        <v>-1.5933</v>
+        <v>-0.3096</v>
       </c>
       <c r="V18" t="n">
-        <v>-2.8223</v>
+        <v>-3.1855</v>
       </c>
       <c r="W18" t="n">
-        <v>2.6805</v>
+        <v>-1.0411</v>
       </c>
       <c r="X18" t="n">
-        <v>-5.502800000000001</v>
+        <v>-2.1444</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>J. BUTLER</t>
+          <t>T. CARTER</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1888,70 +1888,70 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="D19" t="n">
-        <v>-20.0621</v>
+        <v>-15.2771</v>
       </c>
       <c r="E19" t="n">
-        <v>2.424199999999999</v>
+        <v>-15.5248</v>
       </c>
       <c r="F19" t="n">
-        <v>-22.4868</v>
+        <v>0.248</v>
       </c>
       <c r="G19" t="n">
-        <v>20.1471</v>
+        <v>-10.8911</v>
       </c>
       <c r="H19" t="n">
-        <v>9.713800000000001</v>
+        <v>-6.865600000000001</v>
       </c>
       <c r="I19" t="n">
-        <v>10.4333</v>
+        <v>-4.025300000000001</v>
       </c>
       <c r="J19" t="n">
-        <v>47.6217</v>
+        <v>-4.6676</v>
       </c>
       <c r="K19" t="n">
-        <v>23.5469</v>
+        <v>-2.4614</v>
       </c>
       <c r="L19" t="n">
-        <v>24.0748</v>
+        <v>-2.206</v>
       </c>
       <c r="M19" t="n">
-        <v>-27.4748</v>
+        <v>-6.2237</v>
       </c>
       <c r="N19" t="n">
-        <v>-13.8332</v>
+        <v>-4.4041</v>
       </c>
       <c r="O19" t="n">
-        <v>-13.6415</v>
+        <v>-1.8195</v>
       </c>
       <c r="P19" t="n">
-        <v>-26.2106</v>
+        <v>-2.5515</v>
       </c>
       <c r="Q19" t="n">
-        <v>-67.0346</v>
+        <v>-14.3811</v>
       </c>
       <c r="R19" t="n">
-        <v>40.8241</v>
+        <v>11.8297</v>
       </c>
       <c r="S19" t="n">
-        <v>-1.89</v>
+        <v>0.9877999999999999</v>
       </c>
       <c r="T19" t="n">
-        <v>-1.9866</v>
+        <v>0.8429000000000001</v>
       </c>
       <c r="U19" t="n">
-        <v>0.09680000000000019</v>
+        <v>0.1447999999999999</v>
       </c>
       <c r="V19" t="n">
-        <v>-12.1089</v>
+        <v>-2.8223</v>
       </c>
       <c r="W19" t="n">
-        <v>23.8235</v>
+        <v>2.6805</v>
       </c>
       <c r="X19" t="n">
-        <v>-35.9324</v>
+        <v>-5.502800000000001</v>
       </c>
     </row>
     <row r="20">
@@ -1969,13 +1969,13 @@
         <v>24</v>
       </c>
       <c r="D20" t="n">
-        <v>-37.2318</v>
+        <v>-25.6369</v>
       </c>
       <c r="E20" t="n">
-        <v>-36.7533</v>
+        <v>-28.4772</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.4783000000000002</v>
+        <v>2.840399999999999</v>
       </c>
       <c r="G20" t="n">
         <v>-17.5786</v>
@@ -2014,13 +2014,13 @@
         <v>18.0927</v>
       </c>
       <c r="S20" t="n">
-        <v>-6.9655</v>
+        <v>4.6294</v>
       </c>
       <c r="T20" t="n">
-        <v>-5.2068</v>
+        <v>3.0697</v>
       </c>
       <c r="U20" t="n">
-        <v>-1.759</v>
+        <v>1.56</v>
       </c>
       <c r="V20" t="n">
         <v>3.548799999999999</v>
@@ -2047,19 +2047,19 @@
         <v>37</v>
       </c>
       <c r="D21" t="n">
-        <v>79.51149999999998</v>
+        <v>119.5296</v>
       </c>
       <c r="E21" t="n">
-        <v>43.5245</v>
+        <v>55.96590000000002</v>
       </c>
       <c r="F21" t="n">
-        <v>35.9859</v>
+        <v>63.5641</v>
       </c>
       <c r="G21" t="n">
         <v>13.4985</v>
       </c>
       <c r="H21" t="n">
-        <v>9.731499999999999</v>
+        <v>9.731499999999995</v>
       </c>
       <c r="I21" t="n">
         <v>3.768699999999992</v>
@@ -2089,16 +2089,16 @@
         <v>-596.1206999999999</v>
       </c>
       <c r="R21" t="n">
-        <v>562.4883000000001</v>
+        <v>562.4883</v>
       </c>
       <c r="S21" t="n">
-        <v>111.7093</v>
+        <v>151.7271</v>
       </c>
       <c r="T21" t="n">
-        <v>80.68770000000001</v>
+        <v>93.12870000000001</v>
       </c>
       <c r="U21" t="n">
-        <v>31.01990000000001</v>
+        <v>58.59979999999999</v>
       </c>
       <c r="V21" t="n">
         <v>-12.0643</v>
